--- a/data/Data Dictionary.xlsx
+++ b/data/Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46773C05-2007-4046-A505-3F96EDB7B826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA4482F-BD35-ED4D-8B9E-1370386791DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="760" windowWidth="29780" windowHeight="16820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table information" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="248">
   <si>
     <t>Text</t>
   </si>
@@ -604,9 +604,6 @@
   </si>
   <si>
     <t>Steph Eaneff</t>
-  </si>
-  <si>
-    <t>The data dictionary was last updated on 23 April, 2025</t>
   </si>
   <si>
     <t>Raw Costed NAPHS data</t>
@@ -761,6 +758,30 @@
   </si>
   <si>
     <t>The estimated cost, standardized to USD (2024). Data were first converted into USD based on published exchange rates of of December of the specified year, then inflation-adjusted based on the CPI to USD (2024).</t>
+  </si>
+  <si>
+    <t>24 April, 2025</t>
+  </si>
+  <si>
+    <t>Update coding of Liberia core capacity to correctly reflect core capacity "Medical Countermeasures" instead of IPC</t>
+  </si>
+  <si>
+    <t>Liberia Costed NAPHS</t>
+  </si>
+  <si>
+    <t>The data dictionary was last updated on 24 April, 2025</t>
+  </si>
+  <si>
+    <t>Requirement highlights</t>
+  </si>
+  <si>
+    <t>For plots and specific analysis, brief summary statements of specific requirements documented in the file Clean Costed NAPHS data and Raw Costed NAPHS data, interim file created by research team for the purpose of generating figures</t>
+  </si>
+  <si>
+    <t>one row per desired label on a plot</t>
+  </si>
+  <si>
+    <t>Generated by research team</t>
   </si>
 </sst>
 </file>
@@ -1022,27 +1043,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1057,9 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1081,6 +1078,30 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1321,42 +1342,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:22" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="4" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="A4" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -1365,13 +1386,13 @@
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:22" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
     </row>
     <row r="8" spans="1:22" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
@@ -1391,28 +1412,28 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="15" t="s">
         <v>155</v>
       </c>
       <c r="F10" s="2"/>
@@ -1434,13 +1455,13 @@
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1460,19 +1481,19 @@
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="22" t="s">
+      <c r="A12" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="15" t="s">
         <v>155</v>
       </c>
       <c r="F12" s="2"/>
@@ -1494,19 +1515,19 @@
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="15" t="s">
         <v>155</v>
       </c>
       <c r="F13" s="2"/>
@@ -1528,20 +1549,20 @@
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="C14" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="D14" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>215</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>216</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -1561,12 +1582,22 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
     </row>
-    <row r="15" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="2"/>
+    <row r="15" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>247</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -3628,14 +3659,14 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:21" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
@@ -3658,32 +3689,32 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="A4" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G5" s="2"/>
@@ -3703,23 +3734,23 @@
       <c r="U5" s="2"/>
     </row>
     <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>209</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>210</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3738,22 +3769,22 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="D7" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G7" s="2"/>
@@ -3773,22 +3804,22 @@
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G8" s="2"/>
@@ -3808,22 +3839,22 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G9" s="2"/>
@@ -3843,22 +3874,22 @@
       <c r="U9" s="2"/>
     </row>
     <row r="10" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G10" s="2"/>
@@ -3878,22 +3909,22 @@
       <c r="U10" s="2"/>
     </row>
     <row r="11" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G11" s="2"/>
@@ -3913,22 +3944,22 @@
       <c r="U11" s="2"/>
     </row>
     <row r="12" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="D12" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G12" s="2"/>
@@ -3948,22 +3979,22 @@
       <c r="U12" s="2"/>
     </row>
     <row r="13" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" s="22" t="s">
+      <c r="B13" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G13" s="2"/>
@@ -3983,23 +4014,23 @@
       <c r="U13" s="2"/>
     </row>
     <row r="14" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="D14" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>216</v>
+      <c r="F14" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4018,22 +4049,22 @@
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G15" s="2"/>
@@ -4053,32 +4084,32 @@
       <c r="U15" s="2"/>
     </row>
     <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
+      <c r="A16" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
     </row>
     <row r="17" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G17" s="2"/>
@@ -4098,22 +4129,22 @@
       <c r="U17" s="2"/>
     </row>
     <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G18" s="2"/>
@@ -4133,22 +4164,22 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="25" t="s">
+      <c r="A19" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G19" s="2"/>
@@ -4168,22 +4199,22 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="25" t="s">
+      <c r="A20" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G20" s="2"/>
@@ -4203,22 +4234,22 @@
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G21" s="2"/>
@@ -4238,22 +4269,22 @@
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="A22" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G22" s="2"/>
@@ -4273,22 +4304,22 @@
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="25" t="s">
+      <c r="A23" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G23" s="2"/>
@@ -4308,22 +4339,22 @@
       <c r="U23" s="2"/>
     </row>
     <row r="24" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="25" t="s">
+      <c r="A24" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G24" s="2"/>
@@ -4343,22 +4374,22 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B25" s="22" t="s">
+      <c r="A25" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G25" s="2"/>
@@ -4378,23 +4409,23 @@
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="C26" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="D26" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>207</v>
+      <c r="F26" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4413,23 +4444,23 @@
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="22" t="s">
+      <c r="A27" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>207</v>
+      <c r="F27" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -4448,23 +4479,23 @@
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="29" t="s">
+      <c r="A28" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>207</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4483,23 +4514,23 @@
       <c r="U28" s="2"/>
     </row>
     <row r="29" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="22" t="s">
+      <c r="A29" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>216</v>
+      <c r="F29" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4518,23 +4549,23 @@
       <c r="U29" s="2"/>
     </row>
     <row r="30" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="A30" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>216</v>
+      <c r="F30" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4553,23 +4584,23 @@
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="E31" s="22" t="s">
+      <c r="A31" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F31" s="22" t="s">
-        <v>216</v>
+      <c r="F31" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4588,23 +4619,23 @@
       <c r="U31" s="2"/>
     </row>
     <row r="32" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="E32" s="22" t="s">
+      <c r="A32" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>216</v>
+      <c r="F32" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4623,23 +4654,23 @@
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="E33" s="22" t="s">
+      <c r="A33" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>216</v>
+      <c r="F33" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4662,8 +4693,8 @@
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -4685,8 +4716,8 @@
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -4708,8 +4739,8 @@
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4731,8 +4762,8 @@
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4754,8 +4785,8 @@
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4777,8 +4808,8 @@
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4800,8 +4831,8 @@
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4819,12 +4850,12 @@
       <c r="U40" s="3"/>
     </row>
     <row r="41" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4842,12 +4873,12 @@
       <c r="U41" s="3"/>
     </row>
     <row r="42" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -6165,13 +6196,13 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
@@ -8196,43 +8227,43 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="23" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23" t="s">
+      <c r="B4" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -8249,18 +8280,18 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="23" t="s">
+      <c r="A5" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>216</v>
+      <c r="E5" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -8278,11 +8309,19 @@
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>

--- a/data/Data Dictionary.xlsx
+++ b/data/Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA4482F-BD35-ED4D-8B9E-1370386791DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE771B9D-7271-1442-9949-A5433EBE676B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7480" yWindow="760" windowWidth="29780" windowHeight="16820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table information" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="261">
   <si>
     <t>Text</t>
   </si>
@@ -769,9 +769,6 @@
     <t>Liberia Costed NAPHS</t>
   </si>
   <si>
-    <t>The data dictionary was last updated on 24 April, 2025</t>
-  </si>
-  <si>
     <t>Requirement highlights</t>
   </si>
   <si>
@@ -782,6 +779,48 @@
   </si>
   <si>
     <t>Generated by research team</t>
+  </si>
+  <si>
+    <t>line_item_id</t>
+  </si>
+  <si>
+    <t>Unique ID</t>
+  </si>
+  <si>
+    <t>A unique line-item ID for each country, requirement, activity, and year</t>
+  </si>
+  <si>
+    <t>manually created by research team (SE) during data cleaning</t>
+  </si>
+  <si>
+    <t>Tagged line items</t>
+  </si>
+  <si>
+    <t>25 April, 2025</t>
+  </si>
+  <si>
+    <t>Added unique IDs to each line item in clean dataset, created separate dataset for the purpose of tagging line-items</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Line Items</t>
+  </si>
+  <si>
+    <t>ICT (included in written description)</t>
+  </si>
+  <si>
+    <t>ICT (Information and Communication Technology)</t>
+  </si>
+  <si>
+    <t>30 April, 2025</t>
+  </si>
+  <si>
+    <t>Added some additional definitions</t>
+  </si>
+  <si>
+    <t>The data dictionary was last updated on 30 April, 2025</t>
   </si>
 </sst>
 </file>
@@ -926,7 +965,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,9 +1067,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1045,6 +1081,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1061,23 +1103,17 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1102,6 +1138,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1342,42 +1381,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:22" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="4" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
+      <c r="A4" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
     </row>
     <row r="6" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -1386,54 +1425,54 @@
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:22" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:22" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F10" s="2"/>
@@ -1455,13 +1494,13 @@
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1481,19 +1520,19 @@
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F12" s="2"/>
@@ -1515,19 +1554,19 @@
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F13" s="2"/>
@@ -1549,19 +1588,19 @@
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>215</v>
       </c>
       <c r="F14" s="2"/>
@@ -1583,20 +1622,20 @@
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>246</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>247</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1616,12 +1655,22 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
     </row>
-    <row r="16" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="2"/>
+    <row r="16" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>246</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -3641,7 +3690,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U1003"/>
+  <dimension ref="A1:U1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.19921875" customWidth="1"/>
@@ -3659,98 +3708,83 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:21" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-    </row>
-    <row r="5" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:21" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>209</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3769,23 +3803,23 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="15" t="s">
+      <c r="B7" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>186</v>
+      <c r="F7" s="24" t="s">
+        <v>209</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3804,22 +3838,22 @@
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="B8" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G8" s="2"/>
@@ -3839,22 +3873,22 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="B9" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G9" s="2"/>
@@ -3874,22 +3908,22 @@
       <c r="U9" s="2"/>
     </row>
     <row r="10" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="B10" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G10" s="2"/>
@@ -3909,22 +3943,22 @@
       <c r="U10" s="2"/>
     </row>
     <row r="11" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="E11" s="15" t="s">
+      <c r="B11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G11" s="2"/>
@@ -3944,22 +3978,22 @@
       <c r="U11" s="2"/>
     </row>
     <row r="12" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="15" t="s">
+      <c r="B12" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G12" s="2"/>
@@ -3979,22 +4013,22 @@
       <c r="U12" s="2"/>
     </row>
     <row r="13" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="B13" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G13" s="2"/>
@@ -4013,24 +4047,24 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>215</v>
+      <c r="B14" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>186</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4048,24 +4082,24 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>186</v>
+      <c r="B15" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -4083,68 +4117,68 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
+    <row r="16" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D18" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-    </row>
-    <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G18" s="2"/>
@@ -4164,22 +4198,22 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="15" t="s">
+      <c r="B19" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G19" s="2"/>
@@ -4199,22 +4233,22 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="B20" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G20" s="2"/>
@@ -4234,22 +4268,22 @@
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="15" t="s">
+      <c r="B21" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G21" s="2"/>
@@ -4269,22 +4303,22 @@
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="B22" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G22" s="2"/>
@@ -4304,22 +4338,22 @@
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F23" s="15" t="s">
+      <c r="B23" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G23" s="2"/>
@@ -4339,22 +4373,22 @@
       <c r="U23" s="2"/>
     </row>
     <row r="24" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="15" t="s">
+      <c r="B24" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G24" s="2"/>
@@ -4374,22 +4408,22 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" s="15" t="s">
+      <c r="B25" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G25" s="2"/>
@@ -4409,23 +4443,23 @@
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E26" s="15" t="s">
+      <c r="A26" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>206</v>
+      <c r="F26" s="16" t="s">
+        <v>186</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4444,19 +4478,19 @@
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>201</v>
+      <c r="B27" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>198</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="E27" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>183</v>
       </c>
       <c r="F27" s="21" t="s">
@@ -4479,19 +4513,19 @@
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>202</v>
+      <c r="B28" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>201</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>183</v>
       </c>
       <c r="F28" s="21" t="s">
@@ -4513,24 +4547,24 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>221</v>
+    <row r="29" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>202</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="E29" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>215</v>
+      <c r="F29" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4548,23 +4582,23 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" s="15" t="s">
+      <c r="B30" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G30" s="2"/>
@@ -4584,22 +4618,22 @@
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="15" t="s">
+      <c r="B31" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G31" s="2"/>
@@ -4618,23 +4652,23 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="15" t="s">
+      <c r="B32" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G32" s="2"/>
@@ -4654,22 +4688,22 @@
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="B33" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G33" s="2"/>
@@ -4688,13 +4722,25 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
+    <row r="34" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>215</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -4712,12 +4758,12 @@
       <c r="U34" s="2"/>
     </row>
     <row r="35" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -4735,35 +4781,35 @@
       <c r="U35" s="2"/>
     </row>
     <row r="36" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
     </row>
     <row r="37" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4781,12 +4827,12 @@
       <c r="U37" s="3"/>
     </row>
     <row r="38" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4804,12 +4850,12 @@
       <c r="U38" s="3"/>
     </row>
     <row r="39" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4827,12 +4873,12 @@
       <c r="U39" s="3"/>
     </row>
     <row r="40" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4850,12 +4896,12 @@
       <c r="U40" s="3"/>
     </row>
     <row r="41" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4873,12 +4919,12 @@
       <c r="U41" s="3"/>
     </row>
     <row r="42" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -4896,12 +4942,12 @@
       <c r="U42" s="3"/>
     </row>
     <row r="43" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -5171,7 +5217,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
     </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -5217,7 +5263,29 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
     </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+    </row>
     <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6164,11 +6232,12 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -6186,7 +6255,7 @@
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="36.59765625" customWidth="1"/>
-    <col min="3" max="3" width="38.59765625" customWidth="1"/>
+    <col min="3" max="3" width="46.19921875" customWidth="1"/>
     <col min="4" max="4" width="68.59765625" customWidth="1"/>
     <col min="5" max="5" width="57.59765625" customWidth="1"/>
   </cols>
@@ -6196,38 +6265,46 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="A4" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -6243,9 +6320,9 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -8227,43 +8304,45 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="15" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="16"/>
+      <c r="E4" s="17" t="s">
+        <v>254</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -8280,17 +8359,17 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>215</v>
       </c>
       <c r="F5" s="2"/>
@@ -8309,17 +8388,17 @@
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>242</v>
       </c>
       <c r="F6" s="2"/>
@@ -8338,11 +8417,19 @@
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>254</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -8359,11 +8446,19 @@
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>254</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>

--- a/data/Data Dictionary.xlsx
+++ b/data/Data Dictionary.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/costed-NAPHS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE771B9D-7271-1442-9949-A5433EBE676B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C5E959-97B0-9E40-BF12-9DF3D6C1849F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7480" yWindow="760" windowWidth="29780" windowHeight="16820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="460" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table information" sheetId="2" r:id="rId1"/>
+    <sheet name="File information" sheetId="2" r:id="rId1"/>
     <sheet name="Field information" sheetId="12" r:id="rId2"/>
     <sheet name="Definitions" sheetId="15" r:id="rId3"/>
     <sheet name="Revision history" sheetId="16" r:id="rId4"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="224">
   <si>
     <t>Text</t>
   </si>
@@ -435,9 +435,6 @@
     <t>URL/Website</t>
   </si>
   <si>
-    <t>Data Dictionary - Tables/Datasets</t>
-  </si>
-  <si>
     <t>Field</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
     <t>If you have any questions, please reach out to Steph at steph@eaneffdata.com</t>
   </si>
   <si>
-    <t>Clean Costed NAPHS data</t>
-  </si>
-  <si>
     <t>ad hoc (no routine updates)</t>
   </si>
   <si>
@@ -525,21 +519,12 @@
     <t>Year (calendar)</t>
   </si>
   <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Currency (year)</t>
-  </si>
-  <si>
     <t>Flag</t>
   </si>
   <si>
     <t>The country (IHR Member State) that completed the costed NAPHS</t>
   </si>
   <si>
-    <t>The capacity of the JEE to which the cost corresponds (e.g., "P.8 Immunization") based on JEE 3.0</t>
-  </si>
-  <si>
     <t>The real-world requirement that the cost is intended to support (e.g., "Strengthen the implementation of national immunization plans to improve coverage")</t>
   </si>
   <si>
@@ -552,12 +537,6 @@
     <t>The calendar year that the cost is budgeted to occur during (e.g., "2019")</t>
   </si>
   <si>
-    <t>The yearly cost for the activity reported on the costed NAPHS (e.g,, "1000000")</t>
-  </si>
-  <si>
-    <t>The currency that the cost is reported in in the costed NAPHS, including the year (e.g., "USD (2019)")</t>
-  </si>
-  <si>
     <t>Flags with relevant notes about a given data point, e.g., that it was noted as "no cost" or that numbers don't sum to totals as reported in PDF documents</t>
   </si>
   <si>
@@ -579,12 +558,6 @@
     <t>year_calendar</t>
   </si>
   <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>currency</t>
-  </si>
-  <si>
     <t>flag</t>
   </si>
   <si>
@@ -606,60 +579,15 @@
     <t>Steph Eaneff</t>
   </si>
   <si>
-    <t>Raw Costed NAPHS data</t>
-  </si>
-  <si>
     <t>23 April, 2025</t>
   </si>
   <si>
-    <t>Raw, extracted data of costed line items from publicaly available costed National Action Plans for Health Security, one tab per country</t>
-  </si>
-  <si>
-    <t>Final/Clean data</t>
-  </si>
-  <si>
-    <t>Raw/Interim data</t>
-  </si>
-  <si>
-    <t>Final/clean data</t>
-  </si>
-  <si>
-    <t>Raw/interim data</t>
-  </si>
-  <si>
-    <t>Core capacity mapping</t>
-  </si>
-  <si>
     <t>pillar</t>
   </si>
   <si>
     <t>Pillar</t>
   </si>
   <si>
-    <t>core_capacity</t>
-  </si>
-  <si>
-    <t>core_capacity_original</t>
-  </si>
-  <si>
-    <t>Core capacity</t>
-  </si>
-  <si>
-    <t>Core capacity (original)</t>
-  </si>
-  <si>
-    <t>The pillar of the International Health Regulations (IHR) to which the activity corresponds. One of: Prevent, Detect, Respond, or Other</t>
-  </si>
-  <si>
-    <t>The name of the core capacity, standardized across versions of the Joint External Evaluation (with no numbering scheme)</t>
-  </si>
-  <si>
-    <t>The name of the core capacity as it appeared on the costed NAPHS, based on the version of the JEE used for that particular costing effort</t>
-  </si>
-  <si>
-    <t>manually created by research team (SE)</t>
-  </si>
-  <si>
     <t>The capacity of the JEE to which the cost corresponds, standardized across JEEs (e.g., no numbering or abbreviation)</t>
   </si>
   <si>
@@ -667,21 +595,6 @@
   </si>
   <si>
     <t>manually created by research team (SE) based on capacity</t>
-  </si>
-  <si>
-    <t>File to standardize names of core capacities across versions of the JEE</t>
-  </si>
-  <si>
-    <t>one row per JEE version per capacity</t>
-  </si>
-  <si>
-    <t>Exchange rates</t>
-  </si>
-  <si>
-    <t>File to standardize currencies. First, currencies were converted to USD in the specified year (based on December rates), then adjusted based on the CPI to data as of USD as of December 2024</t>
-  </si>
-  <si>
-    <t>one row per observed currency/year combo in original dataset</t>
   </si>
   <si>
     <t>US Department of Treasury. Fiscal Data, Treasury.gov. Currency Exchange Rates Converter. https://fiscaldata.treasury.gov/currency-exchange-rates-converter/. Accessed 23 April, 2025. 
@@ -691,48 +604,9 @@
     <t>currency_original</t>
   </si>
   <si>
-    <t>currency_updated</t>
-  </si>
-  <si>
-    <t>currency_multiplier</t>
-  </si>
-  <si>
-    <t>data_source</t>
-  </si>
-  <si>
-    <t>currency_conversion_notes</t>
-  </si>
-  <si>
     <t>Currency (original)</t>
   </si>
   <si>
-    <t>Currency (updated)</t>
-  </si>
-  <si>
-    <t>Currency multiplier</t>
-  </si>
-  <si>
-    <t>Data source (currency)</t>
-  </si>
-  <si>
-    <t>Notes (currency conversion)</t>
-  </si>
-  <si>
-    <t>The original currency reported on the costed NAPHS that is being converted to a standardized currency, first based on exchange rate data from the US Department of Treasury in December of the specified year, then inflation-adjusted based on the Consumer Price Index to USD (2024), as of December 2024.</t>
-  </si>
-  <si>
-    <t>The updated currency based on the methods described above, standardized to USD (2024) based on data as of December 31, 2024.</t>
-  </si>
-  <si>
-    <t>The multiplier needed to convert the original currency to the updated currency, based on the methods described above. Original costs were first converted to USD as of December of the specified year based on published exchange rates, then inflation adjusted based on the CPI to USD (2024).</t>
-  </si>
-  <si>
-    <t>The data sources used to estimate the currency multiplier used to standardized costs across currencies and years</t>
-  </si>
-  <si>
-    <t>Notes on the data sources amd methods used to estimate the currency multiplier used to standardized costs across currencies and years</t>
-  </si>
-  <si>
     <t>Added fields corresponding to raw data files, renamed column "Action" to "Activity" in raw data files, for consistency; added currency conversion estimates to datasets and documentation</t>
   </si>
   <si>
@@ -769,18 +643,6 @@
     <t>Liberia Costed NAPHS</t>
   </si>
   <si>
-    <t>Requirement highlights</t>
-  </si>
-  <si>
-    <t>For plots and specific analysis, brief summary statements of specific requirements documented in the file Clean Costed NAPHS data and Raw Costed NAPHS data, interim file created by research team for the purpose of generating figures</t>
-  </si>
-  <si>
-    <t>one row per desired label on a plot</t>
-  </si>
-  <si>
-    <t>Generated by research team</t>
-  </si>
-  <si>
     <t>line_item_id</t>
   </si>
   <si>
@@ -793,9 +655,6 @@
     <t>manually created by research team (SE) during data cleaning</t>
   </si>
   <si>
-    <t>Tagged line items</t>
-  </si>
-  <si>
     <t>25 April, 2025</t>
   </si>
   <si>
@@ -820,7 +679,37 @@
     <t>Added some additional definitions</t>
   </si>
   <si>
-    <t>The data dictionary was last updated on 30 April, 2025</t>
+    <t>The data dictionary was last updated on 18 November, 2025</t>
+  </si>
+  <si>
+    <t>File or dataset</t>
+  </si>
+  <si>
+    <t>Line item data.xlsx</t>
+  </si>
+  <si>
+    <t>primary_category</t>
+  </si>
+  <si>
+    <t>primary_subcategory</t>
+  </si>
+  <si>
+    <t>Primary category</t>
+  </si>
+  <si>
+    <t>Primary subcategory</t>
+  </si>
+  <si>
+    <t>Stay tuned!</t>
+  </si>
+  <si>
+    <t>18 November, 2025</t>
+  </si>
+  <si>
+    <t>Simplified data structure, added primary categorization and data for Benin</t>
+  </si>
+  <si>
+    <t>Data Dictionary - Files/Datasets</t>
   </si>
 </sst>
 </file>
@@ -944,7 +833,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -959,18 +848,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00A293"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1007,15 +890,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="8" tint="0.59999389629810485"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1045,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1082,44 +956,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1138,9 +1009,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,7 +1238,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V1006"/>
+  <dimension ref="A1:V999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.796875" customWidth="1"/>
@@ -1381,42 +1249,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="27"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:22" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+    </row>
+    <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-    </row>
-    <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+    </row>
+    <row r="4" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+    </row>
+    <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-    </row>
-    <row r="4" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-    </row>
-    <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -1425,56 +1293,71 @@
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:22" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
+      <c r="A7" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:22" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="C9" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
     </row>
     <row r="10" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>155</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1494,13 +1377,11 @@
       <c r="V10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1520,21 +1401,11 @@
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>155</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1554,21 +1425,11 @@
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>155</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1587,22 +1448,12 @@
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
     </row>
-    <row r="14" spans="1:22" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>215</v>
-      </c>
+    <row r="14" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1621,22 +1472,12 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
     </row>
-    <row r="15" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>246</v>
-      </c>
+    <row r="15" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1655,22 +1496,12 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
     </row>
-    <row r="16" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>246</v>
-      </c>
+    <row r="16" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -1690,8 +1521,8 @@
       <c r="V16" s="2"/>
     </row>
     <row r="17" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1714,8 +1545,8 @@
       <c r="V17" s="2"/>
     </row>
     <row r="18" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -2050,172 +1881,172 @@
       <c r="V31" s="2"/>
     </row>
     <row r="32" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
     </row>
     <row r="33" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
     </row>
     <row r="34" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
     </row>
     <row r="35" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="2"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
     </row>
     <row r="36" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
     </row>
     <row r="37" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
-      <c r="T37" s="2"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="2"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
     </row>
     <row r="38" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
     </row>
     <row r="39" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
@@ -2409,7 +2240,7 @@
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
     </row>
-    <row r="47" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2433,7 +2264,7 @@
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
     </row>
-    <row r="48" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2457,7 +2288,7 @@
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
     </row>
-    <row r="49" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2481,7 +2312,7 @@
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
     </row>
-    <row r="50" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2505,7 +2336,7 @@
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
     </row>
-    <row r="51" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2529,7 +2360,7 @@
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
     </row>
-    <row r="52" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2553,174 +2384,13 @@
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
     </row>
-    <row r="53" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-    </row>
-    <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-    </row>
-    <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="3"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-    </row>
-    <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="3"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-    </row>
-    <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-    </row>
+    <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="61" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="62" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3661,17 +3331,8 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A11:E11"/>
+  <mergeCells count="6">
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
@@ -3690,7 +3351,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U1004"/>
+  <dimension ref="A1:U987"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.19921875" customWidth="1"/>
@@ -3708,83 +3369,108 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:21" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="A2" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-    </row>
-    <row r="5" spans="1:21" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>247</v>
+        <v>167</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>249</v>
+        <v>161</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>250</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
     <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>186</v>
+      <c r="F6" s="24" t="s">
+        <v>185</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3804,22 +3490,22 @@
     </row>
     <row r="7" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>198</v>
+        <v>215</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>155</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>209</v>
+        <v>174</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>177</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3839,22 +3525,22 @@
     </row>
     <row r="8" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>157</v>
+        <v>169</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>156</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -3874,22 +3560,22 @@
     </row>
     <row r="9" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -3909,22 +3595,22 @@
     </row>
     <row r="10" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>177</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>186</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -3944,22 +3630,22 @@
     </row>
     <row r="11" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>160</v>
+        <v>172</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>159</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -3979,22 +3665,22 @@
     </row>
     <row r="12" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -4014,22 +3700,22 @@
     </row>
     <row r="13" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>233</v>
+        <v>187</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -4047,21 +3733,21 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>186</v>
@@ -4084,23 +3770,19 @@
     </row>
     <row r="15" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>215</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -4117,25 +3799,21 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>182</v>
+        <v>215</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>217</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>186</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -4152,35 +3830,48 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
+    <row r="17" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
     </row>
     <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>186</v>
-      </c>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -4198,24 +3889,12 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>186</v>
-      </c>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -4233,583 +3912,403 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
     </row>
     <row r="21" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
     </row>
     <row r="22" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
     </row>
     <row r="23" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
     </row>
     <row r="24" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
     </row>
     <row r="25" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
     </row>
     <row r="26" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
     </row>
     <row r="27" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
     </row>
     <row r="28" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
     </row>
     <row r="29" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-    </row>
-    <row r="30" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="2"/>
-    </row>
-    <row r="31" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-    </row>
-    <row r="32" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-    </row>
-    <row r="33" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-    </row>
-    <row r="34" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+    </row>
+    <row r="30" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+    </row>
+    <row r="31" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+    </row>
+    <row r="32" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+    </row>
+    <row r="33" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+    </row>
+    <row r="34" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
     </row>
     <row r="35" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
     </row>
     <row r="36" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
     </row>
     <row r="37" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4827,12 +4326,12 @@
       <c r="U37" s="3"/>
     </row>
     <row r="38" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4849,13 +4348,13 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
     </row>
-    <row r="39" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4872,13 +4371,13 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
     </row>
-    <row r="40" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4895,404 +4394,30 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
     </row>
-    <row r="41" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-    </row>
-    <row r="42" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-    </row>
-    <row r="43" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-    </row>
-    <row r="44" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-    </row>
-    <row r="45" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-    </row>
-    <row r="46" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-    </row>
-    <row r="47" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-    </row>
-    <row r="48" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-    </row>
-    <row r="49" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-    </row>
-    <row r="50" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-    </row>
-    <row r="51" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-    </row>
-    <row r="52" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-    </row>
-    <row r="53" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-    </row>
-    <row r="54" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-    </row>
-    <row r="55" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="3"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-    </row>
-    <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6216,28 +5341,9 @@
     <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -6265,45 +5371,45 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+    </row>
+    <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-    </row>
-    <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="33"/>
+      <c r="A4" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="21"/>
       <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -6320,9 +5426,9 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -8304,44 +7410,44 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="A2" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>146</v>
-      </c>
       <c r="E3" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -8360,17 +7466,17 @@
     </row>
     <row r="5" spans="1:19" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -8389,17 +7495,17 @@
     </row>
     <row r="6" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -8418,17 +7524,17 @@
     </row>
     <row r="7" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>252</v>
+        <v>205</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -8447,17 +7553,17 @@
     </row>
     <row r="8" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="17" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -8475,11 +7581,19 @@
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>207</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>

--- a/data/Data Dictionary.xlsx
+++ b/data/Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0513CE0C-D7DB-9E4E-89D9-A4D86D9E7806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FA7F8D-54E8-0947-9341-3B379495179E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="460" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="460" yWindow="760" windowWidth="29780" windowHeight="16820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File information" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Hidden_Agencies" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet name="Hidden_DataTypes" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="247">
   <si>
     <t>Text</t>
   </si>
@@ -586,12 +586,6 @@
   </si>
   <si>
     <t>The capacity of the JEE to which the cost corresponds, standardized across JEEs (e.g., no numbering or abbreviation)</t>
-  </si>
-  <si>
-    <t>The pillar of the JEE to which the cost corresponds, based on the capacity specified below</t>
-  </si>
-  <si>
-    <t>manually created by research team (SE) based on capacity</t>
   </si>
   <si>
     <t>US Department of Treasury. Fiscal Data, Treasury.gov. Currency Exchange Rates Converter. https://fiscaldata.treasury.gov/currency-exchange-rates-converter/. Accessed 23 April, 2025. 
@@ -676,9 +670,6 @@
     <t>Added some additional definitions</t>
   </si>
   <si>
-    <t>The data dictionary was last updated on 18 November, 2025</t>
-  </si>
-  <si>
     <t>File or dataset</t>
   </si>
   <si>
@@ -769,14 +760,86 @@
     <t>Data extracted from publicly available NAPHS. While Australia completed a publicly available NAPHS, it did not contain any costs (either line-item or summary) and so it is not represented in this dataset.</t>
   </si>
   <si>
-    <t>Afghanistan, Benin, Eritrea</t>
+    <r>
+      <t xml:space="preserve">Afghanistan, Benin, Eritrea,  Liberia, Myanmar, Nigeria, Sierra Leone, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t>South Sudan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF014D45"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t xml:space="preserve"> Sri Lanka</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF014D45"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t>Tanzania</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Source Sans 3"/>
+      </rPr>
+      <t>, Timor-Leste, Uganda</t>
+    </r>
+  </si>
+  <si>
+    <t>The data dictionary was last updated on 29 December, 2025</t>
+  </si>
+  <si>
+    <t>29 December, 2025</t>
+  </si>
+  <si>
+    <t>Added additional summary cost data points ( Liberia, Myanmar, Nigeria, Sierra Leone, South Sudan, Sri Lanka, Tanzania, Timor-Leste, Uganda)</t>
+  </si>
+  <si>
+    <t>The pillar of the JEE to which the cost corresponds, based on the core capacity specified below</t>
+  </si>
+  <si>
+    <t>Pillars defined based on JEE framework</t>
+  </si>
+  <si>
+    <t>US Department of Treasury. Fiscal Data, Treasury.gov. Currency Exchange Rates Converter. https://fiscaldata.treasury.gov/currency-exchange-rates-converter/. Accessed 23 April, 2025. 
+US Bureau of Labor Statistics. CPI Inflation Calculator. https://www.bls.gov/data/inflation_calculator.htm. Accessed 23 April, 2025.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -898,6 +961,18 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Source Sans 3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Source Sans 3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF014D45"/>
       <name val="Source Sans 3"/>
     </font>
   </fonts>
@@ -1101,8 +1176,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF014D45"/>
       <color rgb="FF00A293"/>
-      <color rgb="FF014D45"/>
       <color rgb="FF083F88"/>
       <color rgb="FF009BDF"/>
       <color rgb="FF9C1C28"/>
@@ -1359,7 +1434,7 @@
     </row>
     <row r="4" spans="1:23" ht="22" customHeight="1">
       <c r="A4" s="35" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
@@ -1384,7 +1459,7 @@
     </row>
     <row r="7" spans="1:23" ht="37" customHeight="1" thickBot="1">
       <c r="A7" s="32" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
@@ -1394,7 +1469,7 @@
     </row>
     <row r="8" spans="1:23" ht="32.25" customHeight="1" thickTop="1">
       <c r="A8" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>2</v>
@@ -1403,7 +1478,7 @@
         <v>150</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>133</v>
@@ -1414,16 +1489,16 @@
     </row>
     <row r="9" spans="1:23" ht="40" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>151</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E9" s="15" t="s">
         <v>149</v>
@@ -1449,18 +1524,18 @@
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
     </row>
-    <row r="10" spans="1:23" ht="40" customHeight="1">
+    <row r="10" spans="1:23" ht="56" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>149</v>
@@ -3532,7 +3607,7 @@
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickTop="1">
       <c r="A3" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>132</v>
@@ -3552,27 +3627,27 @@
     </row>
     <row r="4" spans="1:21" s="16" customFormat="1" ht="46" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>200</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>202</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>174</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>166</v>
@@ -3607,7 +3682,7 @@
     </row>
     <row r="6" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>180</v>
@@ -3616,13 +3691,13 @@
         <v>181</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>173</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
@@ -3642,7 +3717,7 @@
     </row>
     <row r="7" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>167</v>
@@ -3677,7 +3752,7 @@
     </row>
     <row r="8" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A8" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>168</v>
@@ -3712,7 +3787,7 @@
     </row>
     <row r="9" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>169</v>
@@ -3747,7 +3822,7 @@
     </row>
     <row r="10" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A10" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>170</v>
@@ -3782,7 +3857,7 @@
     </row>
     <row r="11" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>171</v>
@@ -3817,16 +3892,16 @@
     </row>
     <row r="12" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B12" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>190</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>192</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>175</v>
@@ -3852,16 +3927,16 @@
     </row>
     <row r="13" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A13" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>173</v>
@@ -3887,22 +3962,22 @@
     </row>
     <row r="14" spans="1:21" s="16" customFormat="1" ht="84" customHeight="1">
       <c r="A14" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B14" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>194</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>196</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>175</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
@@ -3922,16 +3997,16 @@
     </row>
     <row r="15" spans="1:21" s="16" customFormat="1" ht="84" customHeight="1">
       <c r="A15" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>217</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
@@ -3953,16 +4028,16 @@
     </row>
     <row r="16" spans="1:21" s="16" customFormat="1" ht="84" customHeight="1">
       <c r="A16" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B16" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>216</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>219</v>
       </c>
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
@@ -3984,7 +4059,7 @@
     </row>
     <row r="17" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A17" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>172</v>
@@ -3999,7 +4074,7 @@
         <v>173</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
@@ -4019,22 +4094,22 @@
     </row>
     <row r="18" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>225</v>
-      </c>
       <c r="C18" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>174</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
@@ -4054,7 +4129,7 @@
     </row>
     <row r="19" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A19" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>166</v>
@@ -4069,7 +4144,7 @@
         <v>173</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
@@ -4089,16 +4164,16 @@
     </row>
     <row r="20" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A20" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>173</v>
@@ -4124,16 +4199,16 @@
     </row>
     <row r="21" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A21" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>173</v>
@@ -4157,24 +4232,24 @@
       <c r="T21" s="18"/>
       <c r="U21" s="18"/>
     </row>
-    <row r="22" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
+    <row r="22" spans="1:21" s="16" customFormat="1" ht="73" customHeight="1">
       <c r="A22" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B22" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>194</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>196</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>175</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
@@ -4194,16 +4269,16 @@
     </row>
     <row r="23" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A23" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B23" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>190</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>192</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>175</v>
@@ -4229,16 +4304,16 @@
     </row>
     <row r="24" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A24" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>173</v>
@@ -4264,22 +4339,22 @@
     </row>
     <row r="25" spans="1:21" s="16" customFormat="1" ht="50" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B25" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>231</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>234</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>173</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
@@ -5647,16 +5722,16 @@
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1">
       <c r="A4" s="31" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B4" s="31" t="s">
         <v>156</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="24"/>
@@ -7690,14 +7765,14 @@
         <v>177</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -7719,14 +7794,14 @@
         <v>179</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -7745,17 +7820,17 @@
     </row>
     <row r="6" spans="1:19" ht="50" customHeight="1">
       <c r="A6" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C6" s="28"/>
       <c r="D6" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -7774,17 +7849,17 @@
     </row>
     <row r="7" spans="1:19" ht="50" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -7803,17 +7878,17 @@
     </row>
     <row r="8" spans="1:19" ht="50" customHeight="1">
       <c r="A8" s="29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="28"/>
       <c r="D8" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -7832,17 +7907,17 @@
     </row>
     <row r="9" spans="1:19" ht="50" customHeight="1">
       <c r="A9" s="29" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -7860,11 +7935,19 @@
       <c r="S9" s="12"/>
     </row>
     <row r="10" spans="1:19" ht="50" customHeight="1">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="A10" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
